--- a/results/[all]_#_inv_capacity.xlsx
+++ b/results/[all]_#_inv_capacity.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,24 +501,39 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ttes_hp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>btes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>btes_hp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ites</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ites_ac</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1775635958702366</v>
+        <v>0.5082306679309078</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.3079867787294236</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7036754576025982</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +542,13 @@
         <v>0.31259354256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3197672702204145</v>
+        <v>0.6418552073571947</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06880566916063315</v>
+        <v>0.06993967931654989</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +566,19 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6.860475500947478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36462806499665</v>
+        <v>5.353959991262966</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.03460081675852318</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.307037760342177</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.01195121433877251</v>
       </c>
     </row>
   </sheetData>
@@ -568,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,24 +663,39 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ttes_hp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>btes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>btes_hp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ites</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ites_ac</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1430729555907566</v>
+        <v>3.269909145967465</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.291046710352323</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +704,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2453042104539215</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1617638347164718</v>
+        <v>0.160629824560555</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +728,19 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>19.00153496163835</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>7.573329263593783</v>
+        <v>24.68032951637992</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1115613747089956</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.630919568248254</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.02725635511166577</v>
       </c>
     </row>
   </sheetData>
@@ -706,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,24 +825,39 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ttes_hp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>btes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>btes_hp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ites</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ites_ac</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.147975498210015</v>
+        <v>2.305846237445313</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.52533660296037</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +866,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0051421780729205</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1187782292700242</v>
+        <v>0.1186690428607871</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +887,22 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.004524989884599</v>
       </c>
       <c r="N2" t="n">
-        <v>22.14562452588611</v>
+        <v>0.03617967007082259</v>
       </c>
       <c r="O2" t="n">
-        <v>5.634705290485954</v>
+        <v>24.3993217378104</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1351719968364805</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.63983788362259</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.02022198619357558</v>
       </c>
     </row>
   </sheetData>
@@ -844,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,12 +987,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ttes_hp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>btes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>btes_hp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ites</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ites_ac</t>
         </is>
       </c>
     </row>
@@ -968,6 +1055,15 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>13.41050860233228</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -982,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,21 +1149,36 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ttes_hp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>btes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>btes_hp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ites</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ites_ac</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3789801825179429</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01049427933917441</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1103,10 +1214,19 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>24.94925541219651</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.670845117402017</v>
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.670988451873519</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.007358259127211449</v>
       </c>
     </row>
   </sheetData>
@@ -1120,7 +1240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,12 +1311,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ttes_hp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>btes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>btes_hp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ites</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ites_ac</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4.584565170482576</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1244,6 +1379,15 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
       </c>
     </row>
